--- a/supplementary/ESM_3.xlsx
+++ b/supplementary/ESM_3.xlsx
@@ -432,7 +432,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Article title: Edge-level causal graph comparison across 33 TCGA cohorts reveals tissue-specific regulatory structure and prognostic hub genes</t>
+          <t>Article title: A CXCL9–CXCL10–CXCL11 chemokine cascade is the only reproducible cross-cancer causal chain across 33 TCGA cohorts</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Article title: Edge-level causal graph comparison across 33 TCGA cohorts reveals tissue-specific regulatory structure and prognostic hub genes</t>
+          <t>Article title: A CXCL9–CXCL10–CXCL11 chemokine cascade is the only reproducible cross-cancer causal chain across 33 TCGA cohorts</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Article title: Edge-level causal graph comparison across 33 TCGA cohorts reveals tissue-specific regulatory structure and prognostic hub genes</t>
+          <t>Article title: A CXCL9–CXCL10–CXCL11 chemokine cascade is the only reproducible cross-cancer causal chain across 33 TCGA cohorts</t>
         </is>
       </c>
     </row>

--- a/supplementary/ESM_3.xlsx
+++ b/supplementary/ESM_3.xlsx
@@ -432,7 +432,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Article title: A CXCL9–CXCL10–CXCL11 chemokine cascade is the only reproducible cross-cancer causal chain across 33 TCGA cohorts</t>
+          <t>Article title: Panel alignment is a precondition for cross-cancer causal comparison: the reproducible structure across 33 TCGA cohorts is a microenvironmental chemokine axis</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Article title: A CXCL9–CXCL10–CXCL11 chemokine cascade is the only reproducible cross-cancer causal chain across 33 TCGA cohorts</t>
+          <t>Article title: Panel alignment is a precondition for cross-cancer causal comparison: the reproducible structure across 33 TCGA cohorts is a microenvironmental chemokine axis</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Article title: A CXCL9–CXCL10–CXCL11 chemokine cascade is the only reproducible cross-cancer causal chain across 33 TCGA cohorts</t>
+          <t>Article title: Panel alignment is a precondition for cross-cancer causal comparison: the reproducible structure across 33 TCGA cohorts is a microenvironmental chemokine axis</t>
         </is>
       </c>
     </row>

--- a/supplementary/ESM_3.xlsx
+++ b/supplementary/ESM_3.xlsx
@@ -432,7 +432,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Article title: Panel alignment is a precondition for cross-cancer causal comparison: the reproducible structure across 33 TCGA cohorts is a microenvironmental chemokine axis</t>
+          <t>Article title: What is shared across 33 cancer types is the tissue, not the tumour: a non-malignant axis recovered only from aligned gene panels</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Article title: Panel alignment is a precondition for cross-cancer causal comparison: the reproducible structure across 33 TCGA cohorts is a microenvironmental chemokine axis</t>
+          <t>Article title: What is shared across 33 cancer types is the tissue, not the tumour: a non-malignant axis recovered only from aligned gene panels</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Article title: Panel alignment is a precondition for cross-cancer causal comparison: the reproducible structure across 33 TCGA cohorts is a microenvironmental chemokine axis</t>
+          <t>Article title: What is shared across 33 cancer types is the tissue, not the tumour: a non-malignant axis recovered only from aligned gene panels</t>
         </is>
       </c>
     </row>

--- a/supplementary/ESM_3.xlsx
+++ b/supplementary/ESM_3.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shared &gt;=3 cancers" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DepMap concordance" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hub tissue specificity" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="non-malignant markers" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2638,4 +2639,452 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Article title: What is shared across 33 cancer types is the tissue, not the tumour: a non-malignant axis recovered only from aligned gene panels</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Journal: Functional &amp; Integrative Genomics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Author: Shuaidong Gao</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Affiliation: Chongqing Institute of Foreign Studies, Qijiang Campus, Chongqing 401420, China</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Corresponding author e-mail: gaoshuaidong@stu.cqifs.edu.cn</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Marker</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Non-malignant compartment marked</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Membership</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PTPRC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>pan-leukocyte (CD45)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CD3D</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>T cell</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CD3E</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>T cell</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CD2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>T / NK cell</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CD19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B cell</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MS4A1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>B cell (CD20)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CD79A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B cell</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CD79B</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B cell</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>COL1A1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>stromal collagen</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>COL1A2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>stromal collagen</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>COL3A1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>stromal collagen</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DCN</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>fibroblast (decorin)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LUM</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>fibroblast (lumican)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>VWF</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>endothelium</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PECAM1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>endothelium (CD31)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ACTA2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>smooth muscle / myofibroblast</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PDGFRB</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>pericyte / fibroblast</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FAP</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>fibroblast activation</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>THY1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>fibroblast (CD90)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CD163</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>macrophage</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CSF1R</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>myeloid</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LYZ</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>myeloid</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>outside the 100-gene panel</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/supplementary/ESM_3.xlsx
+++ b/supplementary/ESM_3.xlsx
@@ -433,14 +433,14 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Article title: What is shared across 33 cancer types is the tissue, not the tumour: a non-malignant axis recovered only from aligned gene panels</t>
+          <t>Article title: What is shared across 33 cancer types is the tissue, not the tumour: a non-malignant axis of the microenvironment</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Journal: Functional &amp; Integrative Genomics</t>
+          <t>Journal: Network Modeling Analysis in Health Informatics and Bioinformatics</t>
         </is>
       </c>
     </row>
@@ -999,14 +999,14 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Article title: What is shared across 33 cancer types is the tissue, not the tumour: a non-malignant axis recovered only from aligned gene panels</t>
+          <t>Article title: What is shared across 33 cancer types is the tissue, not the tumour: a non-malignant axis of the microenvironment</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Journal: Functional &amp; Integrative Genomics</t>
+          <t>Journal: Network Modeling Analysis in Health Informatics and Bioinformatics</t>
         </is>
       </c>
     </row>
@@ -1444,14 +1444,14 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Article title: What is shared across 33 cancer types is the tissue, not the tumour: a non-malignant axis recovered only from aligned gene panels</t>
+          <t>Article title: What is shared across 33 cancer types is the tissue, not the tumour: a non-malignant axis of the microenvironment</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Journal: Functional &amp; Integrative Genomics</t>
+          <t>Journal: Network Modeling Analysis in Health Informatics and Bioinformatics</t>
         </is>
       </c>
     </row>
@@ -2658,14 +2658,14 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Article title: What is shared across 33 cancer types is the tissue, not the tumour: a non-malignant axis recovered only from aligned gene panels</t>
+          <t>Article title: What is shared across 33 cancer types is the tissue, not the tumour: a non-malignant axis of the microenvironment</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Journal: Functional &amp; Integrative Genomics</t>
+          <t>Journal: Network Modeling Analysis in Health Informatics and Bioinformatics</t>
         </is>
       </c>
     </row>
